--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:18</t>
+    <t xml:space="preserve">2026-09-09 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:18</t>
+    <t xml:space="preserve">2026-09-17 13:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>3.11</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>4.51</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>3.71</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.57</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.11</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.51</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3.71</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:44</t>
+    <t xml:space="preserve">2026-09-25 21:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>0.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -553,7 +553,7 @@
         <v>0.69</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37.3</v>
+        <v>37.12</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>0.62</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>24.9</v>
+        <v>25.06</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>0.7</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>20.41</v>
+        <v>20.52</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -619,10 +619,10 @@
         <v>2.35</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.69</v>
+        <v>0.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>29.36</v>
+        <v>29.7</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>0.69</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>24.04</v>
+        <v>24.13</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>0.81</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>23.62</v>
+        <v>23.67</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -691,7 +691,7 @@
         <v>0.69</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>27.71</v>
+        <v>27.76</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>0.74</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>24.92</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-0.39</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-8.84</v>
+        <v>-8.91</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>0.03</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.16</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4.04</v>
+        <v>-4.13</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>1.69</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>56.9</v>
+        <v>56.77</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>1.9</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>76.92</v>
+        <v>76.71</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>1.79</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>65.81</v>
+        <v>65.69</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2024_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:42</t>
+    <t xml:space="preserve">2026-10-05 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
